--- a/PTBR/Lang/PTBR/Game/Race.xlsx
+++ b/PTBR/Lang/PTBR/Game/Race.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H92"/>
+  <dimension ref="A1:H97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col collapsed="1" width="16" customWidth="1" min="1" max="1"/>
@@ -505,14 +505,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>Yerles</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
           <t>yerles</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>yerles</t>
-        </is>
-      </c>
       <c r="E3" t="inlineStr">
         <is>
           <t>イエルス</t>
@@ -520,7 +520,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Os Yerles, povo do nascente Novo Reino em Sierre Terre, traçam sua linhagem até escravos que escaparam de Eulderna. Nutrindo um ódio profundamente enraizado pelo império e tudo o que ele representa, eles estabeleceram o ápice das civilizações mecânicas em Sierre. Dotados de uma capacidade de aprendizado elevada e habilidosos no manuseio de armamentos mecanizados, conquistam feitos mais rapidamente do que qualquer outra raça.</t>
+          <t>Os Yerles, povo do crescente Novo Reino em Sierre Terre, remontam sua linhagem aos escravos que fugiram dos Eulderna. Guardando um ódio profundo ao império e a tudo o que ele representa, ergueram em Sierre o auge das civilizações mecânicas. Dotados de uma capacidade de aprendizado aguçada e habilidosos com armamentos mecanizados, conquistam feitos mais rápido que qualquer outra raça.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -562,7 +562,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Uma das nações mais antigas de Sierre Terre, Eulderna domina um vasto conhecimento de magia e armamentos mágicos. Reconhecido e temido como o império do deserto, esse povo carrega um senso arrogante de destino escolhido — acreditam ser os únicos dignos de guiar o rumo do mundo. São perfeccionistas cruéis. Os euldernianos são mestres em magia e artefatos mágicos, sendo ideais para profissões de conjuradores e classes intermediárias.</t>
+          <t>Uma das nações mais antigas de Sierre Terre, os Eulderna dominam um vasto conhecimento de magia e armas mágicas. Reconhecidos e temidos como o império do deserto, carregam um senso de destino escolhido, acreditando que só eles são dignos de guiar o curso do mundo. São perfeccionistas cruéis. Habilidosos com magia e itens mágicos, servem bem a conjuradores e profissões intermediárias.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -604,7 +604,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Delicadas, frágeis e efêmeras, as fadas possuem um poder mágico, evasão e velocidade muito superiores aos dos humanos. São altamente resistentes a quase todos os elementos. No entanto, sua fragilidade física impede o uso de equipamentos mais pesados que 1s, tornando a defesa um verdadeiro desafio. Um único golpe físico mais forte pode colocá-las em perigo imediato.</t>
+          <t>Delicadas, frágeis e efêmeras, as fadas ostentam mais poder mágico, esquiva e uma velocidade sem igual comparadas aos humanos. Têm alta resistência a quase todos os elementos. Porém, a fragilidade física as impede de vestir equipamento mais pesado que 1s, o que torna reforçar a defesa um desafio. Um único ataque físico forte pode colocá-las em perigo.</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -631,7 +631,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Povo do Vale</t>
+          <t>Povo das Colinas</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>De baixa estatura, porém robustos e resistentes, os Hillfolk são uma raça determinada. No passado, construíram magníficas cidades de ouro e pedras preciosas sob a terra, agora em ruínas tomadas por monstros perigosos. Com habilidades avançadas em mineração e forja, seus corpos compactos são perfeitos para ambientes escuros e tóxicos. Amam bebidas alcoólicas e, quando embriagados, despertam uma força muito além do normal.</t>
+          <t>O Povo das Colinas é uma raça atarracada e resistente de baixa estatura. Outrora ergueram grandes cidades de ouro e gemas nas profundezas da terra, mas muito desse esplendor hoje sobrevive apenas como ruínas habitadas por monstros perigosos. Com habilidades avançadas de mineração e artesanato, seus corpos compactos e robustos estão equipados para prosperar nos ambientes mais escuros e tóxicos. Têm um amor profundo por álcool e conseguem invocar forças além do normal quando bebem.</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -688,7 +688,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nômades de South Tyris sem terra natal, os Juere muitas vezes se envolvem com bandidagem, o que lhes rendeu má fama em Tyris. Valorizam acima de tudo a liberdade, desprezam restrições e vivem segundo suas próprias regras. Com mãos ágeis, sentidos apurados e uma impressionante capacidade de aprender, são verdadeiros faz-tudo. Vivem de apresentações e conseguem se virar com muito pouco.</t>
+          <t>Nômades de Tyris do Sul sem pátria, os Juere frequentemente derivam para o banditismo, o que os tornou notórios em Tyris. Prezam a liberdade, detestam amarras e priorizam a autonomia pessoal. Com mãos destrosas, sentidos aguçados e alta capacidade de aprendizado, são mestres de todos os ofícios. Dão o sustento com apresentações e sobrevivem com o mínimo de sustento.</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Entre as raças mais antigas e misteriosas de Sierre Terre, os Elea são seres serenos, místicos e belos. Preferem a solidão e vivem em harmonia nas florestas. Têm alta resistência ao éter e vasto poder mágico, capazes até de suavizar os efeitos colaterais da magia.</t>
+          <t>Entre as raças mais antigas e misteriosas de Sierre Terre, os Elea são seres serenos, místicos e belos. Preferindo o isolamento, vivem em paz nas florestas. Têm resistência ao éter e vastos poderes mágicos, com capacidade de mitigar o dano de contra-ataques mágicos.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Pouco se sabe sobre os Formas do Caos, também chamados de "Deformados". Mal conservam uma forma humana. Conforme crescem, adquirem novos membros e partes do corpo, mas suas transformações são completamente imprevisíveis.</t>
+          <t>Pouco se sabe sobre a Forma do Caos, também chamados de "Deformados". Mal conservam uma forma humana. As Formas do Caos ganham novas partes do corpo conforme crescem, mas o que emerge é imprevisível.</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -814,7 +814,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Criatura absurdamente lenta, frágil, fraca e desajeitada, o caracol também não tem nenhuma aptidão para aprendizado. E, claro… pode ser dissolvido com sal.</t>
+          <t>O caracol é uma criatura notavelmente lenta. Frágil, fraco, desengonçado e desprovido de aptidão para aprender, pode ser dissolvido por sal.</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -841,7 +841,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Liche</t>
+          <t>Lich</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mortos-vivos imortais dotados de inteligência e poder mágico imensos, os Liches possuem mais mana e habilidade de meditação do que qualquer outra raça. Porém, carecem de vigor físico para o combate corpo a corpo. Embora resistam a vários elementos, são extremamente vulneráveis ao fogo.</t>
+          <t>Mortos-vivos imortais dotados de enorme inteligência e magia, os Liches possuem mais mana e perícia de meditação que as outras raças. Porém, lhes falta vigor físico para combate direto. Enquanto os liches resistem a vários elementos, são vulneráveis ao fogo.</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Semelhantes aos Liches, os Espectros são mortos-vivos imortais com grande domínio mágico e mental. Possuem alta mana e meditação, mas são frágeis fisicamente. Também têm resistência a diversos elementos, mas o fogo é sua fraqueza fatal.</t>
+          <t>Mortos-vivos imortais dotados de enorme inteligência e magia, os Espectros possuem mais mana e perícia de meditação que as outras raças. Porém, lhes falta vigor físico para combate direto. Enquanto os espectros resistem a vários elementos, são vulneráveis ao fogo.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -940,7 +940,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Criaturas feitas de matéria inanimada animada por magia, os Golems possuem força física incomparável. No entanto, em troca, são extremamente lentos e quase sem mana. Têm alta resistência a veneno, são imunes a sangramentos e não ficam atordoados.</t>
+          <t>Golems são materiais imbuídos de vida por meios mágicos. Comparados às outras raças, ostentam força física muito superior. Porém, talvez como contrapartida, sua mana e velocidade são notavelmente inferiores. Golems têm forte resistência a veneno, são imunes a sangramento e têm a vantagem de não sucumbir ao atordoamento.</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Raça híbrida de humanos com raposas, os Mifu vivem pacificamente em um canto remoto de Tyris. Ao contrário de seus "irmãos", os Nefu, têm pelos e cabelos brancos, além de grandes orelhas fofas que ficam sempre em pé. São brincalhões e alegres. Embora não sejam resistentes, compensam com um domínio impressionante sobre bênçãos e maldições.</t>
+          <t>Os Mifu são uma raça híbrida de raposa e humano que vive quieta num canto de Tyris. Diferente da raça irmã, os Nefu, caracterizam-se pelos pelos brancos e pelas grandes orelhas fofas que ficam em pé. São alegres e marotos, e embora não sejam nada resistentes, compensam com seu conhecimento notável de bênçãos e maldições.</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Com pelos e cabelos avermelhados, seios fartos e caudas que aumentam em número conforme envelhecem, os Nefu também são uma raça híbrida de humano com raposa. Vivem longe de assentamentos humanos, como os Mifu, mas sua beleza exótica e estilo de combate mágico os tornaram objeto de fascínio entre aventureiros.</t>
+          <t>Com pelos vermelhos, seios fartos e caudas fofas que aumentam em número com a idade, os Nefu são uma raça híbrida de raposa e humano. Como os Mifu, moram longe dos assentamentos humanos. Sua beleza marcante, unida ao estilo de combate espada-magia, virou tema de fascínio entre aventureiros.</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1066,7 +1066,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Conhecidas como “Lunares” ou “Filhas da Lua”, as Succubus dizem aparecer ao lado da cama de alguém em noites de luar, seduzindo com seu charme. Na prática, com ou sem lua, de dia ou de noite, elas simplesmente amam experiências prazerosas. Carismáticas e mágicas, tornam-se mais poderosas ao se entregarem aos prazeres da vida.</t>
+          <t>Conhecidas pelos apelidos "Lunar" ou "Parentes do Luar", dizem que as Súcubos aparecem à beira da cama em belas noites de lua, tentando humanos com seu encanto. Na real, com lua ou sem lua, noite ou dia, elas simplesmente adoram experiências prazerosas. Têm carisma e magia altos, ficando mais fortes ao se entregarem às sensações de prazer.</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Os vampiros há muito são temidos como soberanos da noite, dotados tanto de proeza física excepcional quanto intelecto aguçado. Eles demonstram habilidades extraordinárias sob o manto da escuridão, mas permanecem vulneráveis à luz do sol e ao fogo. Incapazes de se sustentar com comida comum, vivem eternamente famintos por sangue fresco e vivo.</t>
+          <t>Vampiros há muito são temidos como senhores da noite, dotados de proeza física excepcional e intelecto afiado. Mostram habilidades extraordinárias sob o manto da escuridão, mas continuam vulneráveis à luz do sol e às chamas. Incapazes de se sustentar de comida comum, sentem fome eterna de sangue fresco e vivo.</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Semideuses são descendentes de uma encarnação divina que desceu à terra e se misturou com os humanos. A maioria deles é fruto dos caprichos dos deuses, sendo raro que descubram suas verdadeiras origens ou habilidades únicas. Possuem uma beleza comparável à dos próprios deuses, habilidades equilibradas, grande vitalidade e mana.</t>
+          <t>Semideuses são a prole de um deus encarnado que desceu à terra e se misturou aos humanos. A maioria é fruto dos caprichos dos deuses, e raramente descobrem suas origens ou suas habilidades únicas. Possuem beleza digna dos deuses, habilidades equilibradas, vitalidade e mana fortes.</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Os centauros são uma raça meio-humana, meio-fera que encarnam tanto um físico poderoso quanto sabedoria. Suas figuras nobres, galopando por terras selvagens e campos de batalha, são celebradas em inúmeras lendas. Embora avessos à feitiçaria, compensam amplamente com sua maestria no arco e flecha. Entre eles, raros indivíduos despertam o "Sétimo Sentido", um dom que concede habilidades muito além de seres comuns, e suas flechas nunca erram o alvo.</t>
+          <t>Centauros são uma raça meio humana, meio besta que encarna física poderosa e sabedoria. Suas figuras nobres, galopando pela natureza selvagem e pelo campo de batalha, foram celebradas em incontáveis contos. Embora torçam o nariz para a feitiçaria, compensam com o domínio do arco e flecha. Entre eles, raros indivíduos despertam o “Sétimo Sentido”, um dom que concede habilidades muito além de seres comuns, e dizem que suas flechas jamais erram o alvo.</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1234,7 +1234,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Apesar de variarem bastante na aparência e nos hábitos, os Shiba são conhecidos por seus corpos robustos e natureza dócil e amigável. Inteligentes e encantadores, também apresentam boa resistência ao frio.</t>
+          <t>Os Shiba, embora diversos em aparência e ecologia, são geralmente conhecidos pela constituição robusta e pela natureza amistosa e submissa. São inteligentes e adoráveis, e têm resistência ao frio.</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>O mais velho entre os caranguejos, o Caranguejo Ancião prefere viver próximo à água e evoluiu de forma distinta conforme o ambiente. Em essência, é delicioso — mas o gosto muda de acordo com seu elemento. São fortes, resistentes, capazes de prender inimigos com suas garras gigantescas e até soltar um sopro de bolhas.</t>
+          <t>O Caranguejo Ancião é o mais velho das espécies de caranguejo, prefere habitats à beira d'água e evolui para vários elementos adaptados ao seu ambiente. São basicamente deliciosos, mas o sabor muda conforme o elemento. Excelentes em força e resistência, podem conter inimigos com suas pinças gigantes e são capazes de expelir um sopro de bolhas.</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1293,88 +1293,88 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>goblin</t>
+          <t>ratkin</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Alpha 15.1</t>
+          <t>EA 23.289</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Goblin</t>
+          <t>Homem-Rato</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>goblin</t>
+          <t>ratkin</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>ゴブリン</t>
+          <t>ラトキン</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>kobolt</t>
+          <t>werewolf</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Alpha 11.1</t>
+          <t>EA 23.293</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Kobold</t>
+          <t>Lobisomem</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>kobold</t>
+          <t>werewolf</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>コボルト</t>
+          <t>人狼</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>orc</t>
+          <t>goblin</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Alpha 11.1</t>
+          <t>Alpha 15.1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Orc</t>
+          <t>Goblin</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>orc</t>
+          <t>goblin</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>オーク</t>
+          <t>ゴブリン</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>troll</t>
+          <t>kobolt</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1384,24 +1384,24 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Troll</t>
+          <t>Kobold</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>troll</t>
+          <t>kobold</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>トロール</t>
+          <t>コボルト</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>lizardman</t>
+          <t>orc</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1411,24 +1411,24 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Homem-Lagarto</t>
+          <t>Orc</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>lizardman</t>
+          <t>orc</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>リザードマン</t>
+          <t>オーク</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>minotaur</t>
+          <t>troll</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1438,24 +1438,24 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Minotauro</t>
+          <t>Troll</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>minotaur</t>
+          <t>troll</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>ミノタウロス</t>
+          <t>トロール</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>norland</t>
+          <t>lizardman</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1465,24 +1465,24 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Norlandês</t>
+          <t>Homem-Lagarto</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>norland</t>
+          <t>lizardman</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>ノーランド</t>
+          <t>リザードマン</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>asura</t>
+          <t>minotaur</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1492,66 +1492,51 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Asura</t>
+          <t>Minotauro</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>asura</t>
+          <t>minotaur</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>阿修羅</t>
+          <t>ミノタウロス</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>slime</t>
+          <t>norland</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>EA 23.278</t>
+          <t>Alpha 11.1</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>slime</t>
+          <t>Norland</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>slime</t>
+          <t>norland</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>スライム</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Slimes são seres amorfos e gelatinosos, com corpos que não possuem forma fixa. Podem parecer frágeis e são frequentemente chamados de os monstros mais fracos, mas possuem um potencial misterioso de absorver tudo o que ingerem e transformá-lo em sua própria força. Mesmo que você um dia acordasse como um slime, não haveria motivo para desespero. Aquele corpo humilde é apenas o começo de um caminho sem fim de evolução.</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Slimes are amorphous, gelatinous beings with bodies that lack a fixed shape. They may appear fragile and are often called the weakest of monsters, yet they possess a mysterious potential to absorb whatever they take in and transform it into their own strength. Even if you were to awaken one day as a slime, there would be no need to despair. That humble body is merely the beginning of an endless path of evolution.</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>スライムは不定形の体を持つ粘体生物です。見た目は頼りなく、最弱の魔物と呼ばれることもありますが、あらゆるものを取り込み、自らの力へと変えていく不思議な可能性を秘めています。もし目覚めたときに自分がスライムだったとしても、嘆く必要はありません。その体は、無限の進化へと続く始まりなのです。</t>
+          <t>ノーランド</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>wolf</t>
+          <t>asura</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1561,51 +1546,66 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Lobo</t>
+          <t>Asura</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>wolf</t>
+          <t>asura</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>狼</t>
+          <t>阿修羅</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>zombie</t>
+          <t>slime</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Alpha 11.1</t>
+          <t>EA 23.278</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Zumbi</t>
+          <t>Gosma</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>zombie</t>
+          <t>slime</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>ゾンビ</t>
+          <t>スライム</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Gosmas são seres amorfos e gelatinosos, com corpos sem forma fixa. Podem parecer frágeis e são muitas vezes chamados dos monstros mais fracos, mas possuem o potencial misterioso de absorver o que quer que engulam e transformá-lo em força própria. Mesmo se você acordasse um dia como uma gosma, não haveria motivo para desespero. Aquele corpo humilde é só o começo de um caminho infinito de evolução.</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Slimes are amorphous, gelatinous beings with bodies that lack a fixed shape. They may appear fragile and are often called the weakest of monsters, yet they possess a mysterious potential to absorb whatever they take in and transform it into their own strength. Even if you were to awaken one day as a slime, there would be no need to despair. That humble body is merely the beginning of an endless path of evolution.</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>スライムは不定形の体を持つ粘体生物です。見た目は頼りなく、最弱の魔物と呼ばれることもありますが、あらゆるものを取り込み、自らの力へと変えていく不思議な可能性を秘めています。もし目覚めたときに自分がスライムだったとしても、嘆く必要はありません。その体は、無限の進化へと続く始まりなのです。</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>rabbit</t>
+          <t>wolf</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1615,24 +1615,24 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Coelho</t>
+          <t>Lobo</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>rabbit</t>
+          <t>wolf</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>ウサギ</t>
+          <t>狼</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>sheep</t>
+          <t>zombie</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1642,24 +1642,24 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Ovelha</t>
+          <t>Zumbi</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>sheep</t>
+          <t>zombie</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>羊</t>
+          <t>ゾンビ</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>frog</t>
+          <t>rabbit</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1669,51 +1669,51 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sapo</t>
+          <t>Coelho</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>frog</t>
+          <t>rabbit</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>蛙</t>
+          <t>ウサギ</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>centipede</t>
+          <t>rabbitkin</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Alpha 11.1</t>
+          <t>EA 23.289</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Centopeia</t>
+          <t>Ravian</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>centipede</t>
+          <t>ravian</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>ムカデ</t>
+          <t>ラビアン</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>mandrake</t>
+          <t>sheep</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1723,51 +1723,51 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Mandrágora</t>
+          <t>Ovelha</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>mandrake</t>
+          <t>sheep</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>マンドレイク</t>
+          <t>羊</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>beetle</t>
+          <t>frog</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>EA 23.27 fix 2</t>
+          <t>Alpha 11.1</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Besouro</t>
+          <t>Sapo</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>beetle</t>
+          <t>frog</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>甲虫</t>
+          <t>蛙</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>mushroom</t>
+          <t>centipede</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1777,24 +1777,24 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Cogumelo</t>
+          <t>Centopeia</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>mushroom</t>
+          <t>centipede</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>きのこ</t>
+          <t>ムカデ</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>bat</t>
+          <t>mandrake</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1804,51 +1804,51 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Morcego</t>
+          <t>Mandrágona</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>bat</t>
+          <t>mandrake</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>コウモリ</t>
+          <t>マンドレイク</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ent</t>
+          <t>beetle</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Alpha 11.1</t>
+          <t>EA 23.27 fix 2</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Ent</t>
+          <t>Besouro</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>ent</t>
+          <t>beetle</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>エント</t>
+          <t>甲虫</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>hound</t>
+          <t>mushroom</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1858,24 +1858,24 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Cão de Caça</t>
+          <t>Cogumelo</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>hound</t>
+          <t>mushroom</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>猟犬</t>
+          <t>きのこ</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ghost</t>
+          <t>bat</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1885,24 +1885,24 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Fantasma</t>
+          <t>Morcego</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>ghost</t>
+          <t>bat</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>幽霊</t>
+          <t>コウモリ</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>spirit</t>
+          <t>ent</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1912,24 +1912,24 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Espírito</t>
+          <t>Ent</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>spirit</t>
+          <t>ent</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>精霊</t>
+          <t>エント</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>eye</t>
+          <t>hound</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1939,24 +1939,24 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Olho</t>
+          <t>Cão de Caça</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>eye</t>
+          <t>hound</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>目</t>
+          <t>猟犬</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>wyvern</t>
+          <t>ghost</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Guiverno</t>
+          <t>Fantasma</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>wyvern</t>
+          <t>ghost</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>ワイバーン</t>
+          <t>幽霊</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>wasp</t>
+          <t>spirit</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1993,24 +1993,24 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Vespa</t>
+          <t>Espírito</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>wasp</t>
+          <t>spirit</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>ワスプ</t>
+          <t>精霊</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>giant</t>
+          <t>eye</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2020,24 +2020,24 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Gigante</t>
+          <t>Olho</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>giant</t>
+          <t>eye</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>巨人</t>
+          <t>目</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>imp</t>
+          <t>wyvern</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2047,24 +2047,24 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Diabrete</t>
+          <t>Wyvern</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>imp</t>
+          <t>wyvern</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>インプ</t>
+          <t>ワイバーン</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>wasp</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2074,24 +2074,24 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Mão</t>
+          <t>Vespa</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>wasp</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>手</t>
+          <t>ワスプ</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>snake</t>
+          <t>giant</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2101,24 +2101,24 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Cobra</t>
+          <t>Gigante</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>snake</t>
+          <t>giant</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>蛇</t>
+          <t>巨人</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>drake</t>
+          <t>imp</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2128,24 +2128,24 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Draco</t>
+          <t>Diabrete</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>drake</t>
+          <t>imp</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>ドレイク</t>
+          <t>インプ</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>bear</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2155,24 +2155,24 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Urso</t>
+          <t>Mão</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>bear</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>熊</t>
+          <t>手</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>armor</t>
+          <t>snake</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2182,24 +2182,24 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Armadura</t>
+          <t>Serpente</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>armor</t>
+          <t>snake</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>鎧</t>
+          <t>蛇</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>medusa</t>
+          <t>drake</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2209,24 +2209,24 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Medusa</t>
+          <t>Drake</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>medusa</t>
+          <t>drake</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>メデューサ</t>
+          <t>ドレイク</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>cupid</t>
+          <t>bear</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2236,24 +2236,24 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Cupido</t>
+          <t>Urso</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>cupid</t>
+          <t>bear</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>キューピット</t>
+          <t>熊</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>phantom</t>
+          <t>armor</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2263,24 +2263,24 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Fantasma Sombrio</t>
+          <t>Armadura</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>phantom</t>
+          <t>armor</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>ファントム</t>
+          <t>鎧</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>harpy</t>
+          <t>medusa</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2290,24 +2290,24 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Hárpia</t>
+          <t>Medusa</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>harpy</t>
+          <t>medusa</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>ハーピー</t>
+          <t>メデューサ</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>dragon</t>
+          <t>cupid</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2317,24 +2317,24 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Dragão</t>
+          <t>Cupido</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>dragon</t>
+          <t>cupid</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>ドラゴン</t>
+          <t>キューピット</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>dinosaur</t>
+          <t>phantom</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2344,24 +2344,24 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Dinossauro</t>
+          <t>Aparição</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>dinosaur</t>
+          <t>phantom</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>恐竜</t>
+          <t>ファントム</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>cerberus</t>
+          <t>harpy</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2371,24 +2371,24 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Cérbero</t>
+          <t>Harpia</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>cerberus</t>
+          <t>harpy</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>ケルベロス</t>
+          <t>ハーピー</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>spider</t>
+          <t>dragon</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2398,24 +2398,24 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Aranha</t>
+          <t>Dragão</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>spider</t>
+          <t>dragon</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>蜘蛛</t>
+          <t>ドラゴン</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>rock</t>
+          <t>dinosaur</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2425,51 +2425,51 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Rocha</t>
+          <t>Dinossauro</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>rock</t>
+          <t>dinosaur</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>岩</t>
+          <t>恐竜</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>crab</t>
+          <t>alien</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Alpha 11.1</t>
+          <t>EA 23.298</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Caranguejo</t>
+          <t>Alienígena</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>crab</t>
+          <t>alien</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>蟹</t>
+          <t>エイリアン</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>skeleton</t>
+          <t>cerberus</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2479,24 +2479,24 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Esqueleto</t>
+          <t>Cérbero</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>skeleton</t>
+          <t>cerberus</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>骸骨</t>
+          <t>ケルベロス</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>piece</t>
+          <t>spider</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2506,24 +2506,24 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Peça</t>
+          <t>Aranha</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>piece</t>
+          <t>spider</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>駒</t>
+          <t>蜘蛛</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>cat</t>
+          <t>rock</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2533,24 +2533,24 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Gato</t>
+          <t>Rocha</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>cat</t>
+          <t>rock</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>猫</t>
+          <t>岩</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>crab</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2560,24 +2560,24 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Cachorro</t>
+          <t>Caranguejo</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>crab</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>犬</t>
+          <t>蟹</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>roran</t>
+          <t>skeleton</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2587,51 +2587,51 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Roran</t>
+          <t>Esqueleto</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>roran</t>
+          <t>skeleton</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>ローラン</t>
+          <t>骸骨</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>mermaid</t>
+          <t>piece</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Alpha 20.64</t>
+          <t>Alpha 11.1</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Sereia</t>
+          <t>Peça</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>mermaid</t>
+          <t>piece</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>人魚</t>
+          <t>駒</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>rat</t>
+          <t>cat</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2641,24 +2641,24 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Rato</t>
+          <t>Gato</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>rat</t>
+          <t>cat</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>ねずみ</t>
+          <t>猫</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>shell</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2668,24 +2668,24 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Concha</t>
+          <t>Cão</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>shell</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>やどかり</t>
+          <t>犬</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>machine</t>
+          <t>roran</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2695,51 +2695,51 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Máquina</t>
+          <t>Roran</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>machine</t>
+          <t>roran</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>機械</t>
+          <t>ローラン</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>wisp</t>
+          <t>mermaid</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Alpha 11.1</t>
+          <t>Alpha 20.64</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Fagulha</t>
+          <t>Sereia</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>wisp</t>
+          <t>mermaid</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>ウィスプ</t>
+          <t>人魚</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>chicken</t>
+          <t>rat</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2749,24 +2749,24 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Galinha</t>
+          <t>Rato</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>chicken</t>
+          <t>rat</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>鶏</t>
+          <t>ねずみ</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>stalker</t>
+          <t>shell</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2776,24 +2776,24 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Perseguidor</t>
+          <t>Concha</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>stalker</t>
+          <t>shell</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>ストーカー</t>
+          <t>やどかり</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>yeek</t>
+          <t>machine</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2803,24 +2803,24 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Yeek</t>
+          <t>Máquina</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>yeek</t>
+          <t>machine</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>イーク</t>
+          <t>機械</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>yith</t>
+          <t>wisp</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2830,51 +2830,51 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Yith</t>
+          <t>Fogo-Fátuo</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>yith</t>
+          <t>wisp</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>イス</t>
+          <t>ウィスプ</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>octopus</t>
+          <t>chicken</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>EA 23.116</t>
+          <t>Alpha 11.1</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Polvo</t>
+          <t>Frango</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>octopus</t>
+          <t>chicken</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>タコ</t>
+          <t>鶏</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>horse</t>
+          <t>stalker</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2884,24 +2884,24 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Cavalo</t>
+          <t>Perseguidor</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>horse</t>
+          <t>stalker</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>馬</t>
+          <t>ストーカー</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>quickling</t>
+          <t>yeek</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Veloz</t>
+          <t>Yeek</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>quickling</t>
+          <t>yeek</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>クイックリング</t>
+          <t>イーク</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>metal</t>
+          <t>yith</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2938,51 +2938,51 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Metal</t>
+          <t>Yith</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>metal</t>
+          <t>yith</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>メタル</t>
+          <t>イス</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>bike</t>
+          <t>octopus</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Alpha 11.1</t>
+          <t>EA 23.116</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Moto</t>
+          <t>Polvo</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>bike</t>
+          <t>octopus</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>バイク</t>
+          <t>タコ</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>fish</t>
+          <t>horse</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2992,51 +2992,51 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Peixe</t>
+          <t>Cavalo</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>fish</t>
+          <t>horse</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>魚</t>
+          <t>馬</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>animal</t>
+          <t>quickling</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Alpha 20.40</t>
+          <t>Alpha 11.1</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Porco</t>
+          <t>Ligeirinho</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>pig</t>
+          <t>quickling</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>豚</t>
+          <t>クイックリング</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>catgod</t>
+          <t>metal</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3046,24 +3046,24 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Deus Gato</t>
+          <t>Metal</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>catgod</t>
+          <t>metal</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>猫の神</t>
+          <t>メタル</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>machinegod</t>
+          <t>bike</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3073,24 +3073,24 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Deus Máquina</t>
+          <t>Moto</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>machinegod</t>
+          <t>bike</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>機械の神</t>
+          <t>バイク</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>undeadgod</t>
+          <t>fish</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3100,123 +3100,258 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Deus dos Mortos</t>
+          <t>Peixe</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>undeadgod</t>
+          <t>fish</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>死霊の神</t>
+          <t>魚</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>catsister</t>
+          <t>animal</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Alpha 11.1</t>
+          <t>Alpha 20.40</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Irmã Gata</t>
+          <t>Porco</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>catsister</t>
+          <t>pig</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>妹猫</t>
+          <t>豚</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>demon</t>
+          <t>catgod</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>EA 23.97</t>
+          <t>Alpha 11.1</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Demônio</t>
+          <t>Deus-Gato</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>demon</t>
+          <t>catgod</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>悪魔</t>
+          <t>猫の神</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>servant</t>
+          <t>machinegod</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Alpha 20.64</t>
+          <t>Alpha 11.1</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Apóstolo</t>
+          <t>Deus-Máquina</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>apostle</t>
+          <t>machinegod</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>使徒</t>
+          <t>機械の神</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
+          <t>undeadgod</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Alpha 11.1</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Deus-Morto-Vivo</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>undeadgod</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>死霊の神</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>catsister</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Alpha 11.1</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Irmã-Gata</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>catsister</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>妹猫</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>demon</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>EA 23.97</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Demônio</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>demon</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>悪魔</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>servant</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Alpha 20.64</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Apóstolo</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>apostle</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>使徒</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
           <t>god</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr">
+      <c r="B96" t="inlineStr">
         <is>
           <t>Alpha 20.27</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr">
+      <c r="C96" t="inlineStr">
         <is>
           <t>Deus</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr">
+      <c r="D96" t="inlineStr">
         <is>
           <t>god</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr">
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>神</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>god_mani</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>EA 23.323</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Deus</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>god</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
         <is>
           <t>神</t>
         </is>
